--- a/Data_Table/상점 테이블.xlsx
+++ b/Data_Table/상점 테이블.xlsx
@@ -845,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -869,20 +869,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>상품 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>등급</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>묶음 수량</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>등장 가중치</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>치즈 가격 (BC)</t>
         </is>
@@ -901,20 +906,25 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>goods_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>grade</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>spawn_weight</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>price_cheese_bc</t>
         </is>
@@ -933,20 +943,25 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -961,18 +976,21 @@
           <t>전설 조각 (소)</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="1" t="n">
+        <v>3590001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="F4" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>360</v>
       </c>
     </row>
@@ -985,18 +1003,21 @@
           <t>전설 조각 (중)</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="1" t="n">
+        <v>3590002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>650</v>
       </c>
     </row>
@@ -1009,18 +1030,21 @@
           <t>전설 조각 (대)</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="1" t="n">
+        <v>3590003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1033,18 +1057,21 @@
           <t>신화 조각 (소)</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="1" t="n">
+        <v>3590011</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>720</v>
       </c>
     </row>
@@ -1057,18 +1084,21 @@
           <t>신화 조각 (중)</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="1" t="n">
+        <v>3590012</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="E8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>1320</v>
       </c>
     </row>
@@ -1081,18 +1111,21 @@
           <t>신화 조각 (대)</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="1" t="n">
+        <v>3590013</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>Mythic</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="E9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>1800</v>
       </c>
     </row>

--- a/Data_Table/상점 테이블.xlsx
+++ b/Data_Table/상점 테이블.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Shop_Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Shop_Slot" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Shop_Goods" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Shop_Floor" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Slot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Goods" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Floor" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>3</v>
+        <v>6.76</v>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
@@ -661,6 +661,36 @@
       <c r="C15" s="1" t="inlineStr">
         <is>
           <t>신화 구매 · 보유 치즈의 이 비율 이상 리롤은 확인 창</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bc_floor_grow</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1.2213</v>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>층 치즈 수입 배율 (gen_economy fit_k) — BC 에 곱함</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>bc_floor_cap</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>층 수입 배율을 이 층까지만</t>
         </is>
       </c>
     </row>
@@ -985,7 +1015,7 @@
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>50</v>
@@ -1012,7 +1042,7 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>35</v>
@@ -1039,7 +1069,7 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>15</v>
@@ -1066,7 +1096,7 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>60</v>
@@ -1093,7 +1123,7 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>30</v>
@@ -1120,7 +1150,7 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>

--- a/Data_Table/상점 테이블.xlsx
+++ b/Data_Table/상점 테이블.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Slot" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Goods" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Floor" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Shop_Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shop_Slot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Shop_Goods" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Shop_Floor" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -691,6 +691,36 @@
       <c r="C17" s="1" t="inlineStr">
         <is>
           <t>층 수입 배율을 이 층까지만</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>goods_reroll_growth</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>유료 리롤 한 번마다 조각 가격 배율 (다음 자동 입고 때 원래대로, 2026-10-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>shard_full_tier</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>조각 묶음 수 = pack_size × 훈장 ÷ 이 값 (이 훈장에서 테이블 값, 최소 1, 2026-10-21)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/상점 테이블.xlsx
+++ b/Data_Table/상점 테이블.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Shop_Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Shop_Slot" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Shop_Goods" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Shop_Floor" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Slot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Goods" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop_Floor" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
